--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7478,0.1032,0.1350,0.0290</t>
-  </si>
-  <si>
-    <t>0.8900,0.0428,0.0216,0.0128</t>
-  </si>
-  <si>
-    <t>0.8040,0.0823,0.0125,0.0159</t>
-  </si>
-  <si>
-    <t>0.9132,0.0523,0.0153,0.0037</t>
-  </si>
-  <si>
-    <t>0.8644,0.0478,0.0113,0.0172</t>
-  </si>
-  <si>
-    <t>0.9111,0.0427,0.0076,0.0096</t>
-  </si>
-  <si>
-    <t>0.8399,0.0531,0.0200,0.0305</t>
-  </si>
-  <si>
-    <t>0.9391,0.0254,0.0065,0.0048</t>
-  </si>
-  <si>
-    <t>0.8626,0.0633,0.0136,0.0174</t>
-  </si>
-  <si>
-    <t>0.7733,0.1677,0.0196,0.0155</t>
-  </si>
-  <si>
-    <t>0.7043,0.1463,0.0153,0.0261</t>
-  </si>
-  <si>
-    <t>0.7849,0.1106,0.0090,0.0151</t>
-  </si>
-  <si>
-    <t>0.9692,0.0107,0.0069,0.0009</t>
-  </si>
-  <si>
-    <t>0.9694,0.0128,0.0085,0.0005</t>
-  </si>
-  <si>
-    <t>0.9818,0.0054,0.0056,0.0005</t>
-  </si>
-  <si>
-    <t>0.7295,0.1255,0.1005,0.0036</t>
-  </si>
-  <si>
-    <t>0.5277,0.4456,0.0316,0.0057</t>
-  </si>
-  <si>
-    <t>0.6603,0.3283,0.0304,0.0036</t>
-  </si>
-  <si>
-    <t>0.6881,0.3717,0.0163,0.0020</t>
-  </si>
-  <si>
-    <t>0.3245,0.6849,0.0189,0.0072</t>
-  </si>
-  <si>
-    <t>0.7908,0.2093,0.0198,0.0017</t>
-  </si>
-  <si>
-    <t>0.2924,0.7400,0.0199,0.0045</t>
-  </si>
-  <si>
-    <t>0.9612,0.0088,0.0186,0.0010</t>
-  </si>
-  <si>
-    <t>0.9709,0.0055,0.0191,0.0007</t>
-  </si>
-  <si>
-    <t>0.9158,0.0345,0.0266,0.0008</t>
-  </si>
-  <si>
-    <t>0.9376,0.0087,0.0512,0.0049</t>
-  </si>
-  <si>
-    <t>0.9302,0.0135,0.0569,0.0019</t>
-  </si>
-  <si>
-    <t>0.9028,0.0298,0.0597,0.0022</t>
-  </si>
-  <si>
-    <t>0.7498,0.0547,0.1958,0.0023</t>
-  </si>
-  <si>
-    <t>0.9260,0.0525,0.0098,0.0020</t>
-  </si>
-  <si>
-    <t>0.9379,0.0364,0.0097,0.0017</t>
-  </si>
-  <si>
-    <t>0.0510,0.2831,0.9045,0.0039</t>
-  </si>
-  <si>
-    <t>0.7345,0.3000,0.0218,0.0012</t>
-  </si>
-  <si>
-    <t>0.8225,0.1556,0.0122,0.0023</t>
-  </si>
-  <si>
-    <t>0.6554,0.2675,0.0552,0.0163</t>
-  </si>
-  <si>
-    <t>0.6130,0.3744,0.0192,0.0078</t>
-  </si>
-  <si>
-    <t>0.8870,0.0909,0.0174,0.0011</t>
-  </si>
-  <si>
-    <t>0.3868,0.5242,0.1976,0.0065</t>
-  </si>
-  <si>
-    <t>0.9365,0.0054,0.0486,0.0124</t>
-  </si>
-  <si>
-    <t>0.9511,0.0079,0.0426,0.0022</t>
-  </si>
-  <si>
-    <t>0.8917,0.0328,0.0695,0.0020</t>
-  </si>
-  <si>
-    <t>0.7256,0.1258,0.1355,0.0020</t>
-  </si>
-  <si>
-    <t>0.5628,0.4964,0.0353,0.0015</t>
-  </si>
-  <si>
-    <t>0.9493,0.0078,0.0429,0.0016</t>
-  </si>
-  <si>
-    <t>0.7904,0.1901,0.0091,0.0022</t>
-  </si>
-  <si>
-    <t>0.4084,0.6793,0.0187,0.0012</t>
-  </si>
-  <si>
-    <t>0.8220,0.2086,0.0112,0.0008</t>
-  </si>
-  <si>
-    <t>0.5934,0.4811,0.0103,0.0011</t>
-  </si>
-  <si>
-    <t>0.0821,0.7541,0.6929,0.0109</t>
-  </si>
-  <si>
-    <t>0.6248,0.2441,0.1230,0.0043</t>
-  </si>
-  <si>
-    <t>0.7589,0.1029,0.1208,0.0053</t>
-  </si>
-  <si>
-    <t>0.8199,0.0614,0.1127,0.0105</t>
-  </si>
-  <si>
-    <t>0.5539,0.0953,0.3813,0.0028</t>
-  </si>
-  <si>
-    <t>0.7701,0.0685,0.1787,0.0022</t>
-  </si>
-  <si>
-    <t>0.6289,0.2411,0.0161,0.0319</t>
-  </si>
-  <si>
-    <t>0.8691,0.0911,0.0163,0.0095</t>
-  </si>
-  <si>
-    <t>0.8544,0.0844,0.0077,0.0070</t>
-  </si>
-  <si>
-    <t>0.4044,0.5240,0.2564,0.0259</t>
-  </si>
-  <si>
-    <t>0.8819,0.0401,0.0063,0.0155</t>
-  </si>
-  <si>
-    <t>0.8766,0.0644,0.0116,0.0130</t>
-  </si>
-  <si>
-    <t>0.7666,0.1399,0.0150,0.0156</t>
-  </si>
-  <si>
-    <t>0.0168,0.9460,0.6807,0.0016</t>
-  </si>
-  <si>
-    <t>0.1402,0.6024,0.6734,0.0043</t>
-  </si>
-  <si>
-    <t>0.7355,0.1114,0.1762,0.0035</t>
-  </si>
-  <si>
-    <t>0.0249,0.8964,0.7350,0.0019</t>
-  </si>
-  <si>
-    <t>0.1195,0.2212,0.8243,0.0009</t>
-  </si>
-  <si>
-    <t>0.8035,0.2216,0.0135,0.0008</t>
-  </si>
-  <si>
-    <t>0.4430,0.7274,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.9375,0.0501,0.0118,0.0012</t>
-  </si>
-  <si>
-    <t>0.9197,0.0282,0.0247,0.0074</t>
-  </si>
-  <si>
-    <t>0.0081,0.8490,0.7917,0.0010</t>
-  </si>
-  <si>
-    <t>0.1060,0.8298,0.2343,0.0028</t>
-  </si>
-  <si>
-    <t>0.0601,0.9116,0.3385,0.0067</t>
-  </si>
-  <si>
-    <t>0.0160,0.9804,0.1423,0.0005</t>
-  </si>
-  <si>
-    <t>0.0398,0.9175,0.4116,0.0009</t>
-  </si>
-  <si>
-    <t>0.9532,0.0069,0.0288,0.0051</t>
-  </si>
-  <si>
-    <t>0.8465,0.0100,0.0160,0.0901</t>
-  </si>
-  <si>
-    <t>0.8818,0.0206,0.0353,0.0458</t>
-  </si>
-  <si>
-    <t>0.9156,0.0297,0.0277,0.0107</t>
-  </si>
-  <si>
-    <t>0.7278,0.1048,0.0833,0.0616</t>
-  </si>
-  <si>
-    <t>0.8747,0.0267,0.0142,0.0395</t>
-  </si>
-  <si>
-    <t>0.0154,0.9173,0.8084,0.0017</t>
-  </si>
-  <si>
-    <t>0.1914,0.6877,0.3379,0.0066</t>
-  </si>
-  <si>
-    <t>0.5492,0.1961,0.2999,0.0031</t>
-  </si>
-  <si>
-    <t>0.3393,0.4650,0.3226,0.0048</t>
-  </si>
-  <si>
-    <t>0.0244,0.9308,0.5901,0.0023</t>
-  </si>
-  <si>
-    <t>0.0113,0.9715,0.4125,0.0015</t>
-  </si>
-  <si>
-    <t>0.8979,0.0564,0.0093,0.0057</t>
-  </si>
-  <si>
-    <t>0.9151,0.0278,0.0103,0.0127</t>
-  </si>
-  <si>
-    <t>0.8891,0.0366,0.0109,0.0227</t>
-  </si>
-  <si>
-    <t>0.8724,0.0459,0.0179,0.0219</t>
-  </si>
-  <si>
-    <t>0.7601,0.0776,0.0162,0.0329</t>
-  </si>
-  <si>
-    <t>0.8582,0.0838,0.0098,0.0056</t>
-  </si>
-  <si>
-    <t>0.8732,0.0793,0.0258,0.0105</t>
-  </si>
-  <si>
-    <t>0.8006,0.1403,0.0279,0.0127</t>
-  </si>
-  <si>
-    <t>0.7976,0.0627,0.0053,0.0200</t>
-  </si>
-  <si>
-    <t>0.8804,0.0754,0.0110,0.0084</t>
-  </si>
-  <si>
-    <t>0.8900,0.0219,0.0048,0.0298</t>
-  </si>
-  <si>
-    <t>0.7881,0.0718,0.0187,0.0475</t>
-  </si>
-  <si>
-    <t>0.8401,0.1026,0.0143,0.0080</t>
-  </si>
-  <si>
-    <t>0.8721,0.0878,0.0105,0.0126</t>
-  </si>
-  <si>
-    <t>0.8863,0.0981,0.0051,0.0027</t>
-  </si>
-  <si>
-    <t>0.9018,0.0523,0.0152,0.0092</t>
-  </si>
-  <si>
-    <t>0.5233,0.0420,0.5861,0.0017</t>
-  </si>
-  <si>
-    <t>0.8963,0.0181,0.0945,0.0015</t>
-  </si>
-  <si>
-    <t>0.9470,0.0194,0.0141,0.0040</t>
-  </si>
-  <si>
-    <t>0.9420,0.0207,0.0153,0.0035</t>
-  </si>
-  <si>
-    <t>0.0745,0.9244,0.0167,0.0068</t>
-  </si>
-  <si>
-    <t>0.5482,0.4963,0.0246,0.0021</t>
-  </si>
-  <si>
-    <t>0.4366,0.6169,0.0132,0.0028</t>
-  </si>
-  <si>
-    <t>0.8174,0.1529,0.0191,0.0079</t>
-  </si>
-  <si>
-    <t>0.6480,0.3524,0.0223,0.0040</t>
-  </si>
-  <si>
-    <t>0.1830,0.8574,0.0068,0.0043</t>
-  </si>
-  <si>
-    <t>0.7979,0.2775,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.9248,0.0250,0.0182,0.0054</t>
-  </si>
-  <si>
-    <t>0.9481,0.0112,0.0398,0.0019</t>
-  </si>
-  <si>
-    <t>0.8097,0.1102,0.0413,0.0085</t>
-  </si>
-  <si>
-    <t>0.9360,0.0357,0.0114,0.0017</t>
-  </si>
-  <si>
-    <t>0.9508,0.0121,0.0210,0.0041</t>
-  </si>
-  <si>
-    <t>0.4005,0.6797,0.0047,0.0015</t>
-  </si>
-  <si>
-    <t>0.4824,0.6332,0.0064,0.0009</t>
-  </si>
-  <si>
-    <t>0.7998,0.1916,0.0077,0.0013</t>
-  </si>
-  <si>
-    <t>0.1808,0.8645,0.0268,0.0003</t>
-  </si>
-  <si>
-    <t>0.6799,0.3257,0.0228,0.0036</t>
-  </si>
-  <si>
-    <t>0.8350,0.1507,0.0094,0.0037</t>
-  </si>
-  <si>
-    <t>0.8469,0.1785,0.0081,0.0016</t>
-  </si>
-  <si>
-    <t>0.9754,0.0183,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9323,0.0376,0.0071,0.0047</t>
-  </si>
-  <si>
-    <t>0.9355,0.0285,0.0034,0.0053</t>
-  </si>
-  <si>
-    <t>0.9317,0.0203,0.0073,0.0147</t>
-  </si>
-  <si>
-    <t>0.7961,0.0669,0.0297,0.0372</t>
-  </si>
-  <si>
-    <t>0.9145,0.0559,0.0082,0.0068</t>
-  </si>
-  <si>
-    <t>0.8469,0.0571,0.0189,0.0437</t>
-  </si>
-  <si>
-    <t>0.6440,0.1811,0.0472,0.0508</t>
-  </si>
-  <si>
-    <t>0.1666,0.7842,0.2016,0.0023</t>
-  </si>
-  <si>
-    <t>0.0569,0.8530,0.4507,0.0011</t>
-  </si>
-  <si>
-    <t>0.5910,0.1928,0.2564,0.0199</t>
-  </si>
-  <si>
-    <t>0.6483,0.2500,0.0872,0.0020</t>
-  </si>
-  <si>
-    <t>0.9807,0.0035,0.0099,0.0007</t>
-  </si>
-  <si>
-    <t>0.8428,0.0951,0.0365,0.0020</t>
-  </si>
-  <si>
-    <t>0.9798,0.0031,0.0140,0.0008</t>
-  </si>
-  <si>
-    <t>0.9797,0.0061,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.8732,0.0582,0.0385,0.0073</t>
-  </si>
-  <si>
-    <t>0.8559,0.0100,0.0242,0.0731</t>
-  </si>
-  <si>
-    <t>0.8662,0.0372,0.0438,0.0339</t>
-  </si>
-  <si>
-    <t>0.9478,0.0112,0.0210,0.0060</t>
-  </si>
-  <si>
-    <t>0.0186,0.8934,0.7147,0.0030</t>
-  </si>
-  <si>
-    <t>0.7781,0.2432,0.0075,0.0022</t>
-  </si>
-  <si>
-    <t>0.6721,0.2922,0.0151,0.0083</t>
-  </si>
-  <si>
-    <t>0.9263,0.0366,0.0095,0.0057</t>
-  </si>
-  <si>
-    <t>0.8242,0.1273,0.0176,0.0086</t>
-  </si>
-  <si>
-    <t>0.8659,0.0446,0.0173,0.0179</t>
-  </si>
-  <si>
-    <t>0.9270,0.0310,0.0065,0.0054</t>
-  </si>
-  <si>
-    <t>0.8028,0.0926,0.0351,0.0288</t>
-  </si>
-  <si>
-    <t>0.0573,0.7951,0.6631,0.0147</t>
-  </si>
-  <si>
-    <t>0.9088,0.0334,0.0078,0.0089</t>
-  </si>
-  <si>
-    <t>0.9533,0.0202,0.0070,0.0046</t>
-  </si>
-  <si>
-    <t>0.7630,0.2563,0.0103,0.0016</t>
-  </si>
-  <si>
-    <t>0.8921,0.0616,0.0099,0.0049</t>
-  </si>
-  <si>
-    <t>0.9734,0.0117,0.0069,0.0007</t>
-  </si>
-  <si>
-    <t>0.9242,0.0356,0.0100,0.0030</t>
-  </si>
-  <si>
-    <t>0.9482,0.0282,0.0078,0.0015</t>
-  </si>
-  <si>
-    <t>0.9542,0.0179,0.0097,0.0022</t>
-  </si>
-  <si>
-    <t>0.9000,0.0385,0.0133,0.0157</t>
-  </si>
-  <si>
-    <t>0.9173,0.0510,0.0066,0.0063</t>
-  </si>
-  <si>
-    <t>0.7919,0.0171,0.0045,0.1021</t>
-  </si>
-  <si>
-    <t>0.8898,0.0661,0.0142,0.0050</t>
-  </si>
-  <si>
-    <t>0.6938,0.2458,0.0506,0.0124</t>
-  </si>
-  <si>
-    <t>0.7744,0.1386,0.0204,0.0239</t>
-  </si>
-  <si>
-    <t>0.9625,0.0177,0.0025,0.0028</t>
-  </si>
-  <si>
-    <t>0.8274,0.0894,0.0236,0.0269</t>
-  </si>
-  <si>
-    <t>0.7997,0.2083,0.0105,0.0024</t>
-  </si>
-  <si>
-    <t>0.6404,0.3115,0.0147,0.0089</t>
-  </si>
-  <si>
-    <t>0.1261,0.9066,0.0053,0.0017</t>
-  </si>
-  <si>
-    <t>0.9760,0.0092,0.0015,0.0014</t>
-  </si>
-  <si>
-    <t>0.8908,0.0644,0.0101,0.0056</t>
-  </si>
-  <si>
-    <t>0.9204,0.0611,0.0042,0.0014</t>
-  </si>
-  <si>
-    <t>0.6727,0.2551,0.0151,0.0105</t>
-  </si>
-  <si>
-    <t>0.8288,0.1597,0.0065,0.0017</t>
-  </si>
-  <si>
-    <t>0.2129,0.3614,0.5961,0.0189</t>
-  </si>
-  <si>
-    <t>0.7857,0.2080,0.0162,0.0053</t>
-  </si>
-  <si>
-    <t>0.6581,0.1690,0.1675,0.0040</t>
-  </si>
-  <si>
-    <t>0.6216,0.1956,0.2093,0.0106</t>
-  </si>
-  <si>
-    <t>0.9698,0.0074,0.0170,0.0008</t>
-  </si>
-  <si>
-    <t>0.5227,0.2632,0.2438,0.0012</t>
-  </si>
-  <si>
-    <t>0.6297,0.2563,0.1051,0.0064</t>
-  </si>
-  <si>
-    <t>0.9177,0.0167,0.0730,0.0013</t>
-  </si>
-  <si>
-    <t>0.7994,0.0635,0.1649,0.0055</t>
-  </si>
-  <si>
-    <t>0.7988,0.1331,0.0401,0.0029</t>
-  </si>
-  <si>
-    <t>0.9636,0.0106,0.0190,0.0011</t>
-  </si>
-  <si>
-    <t>0.8375,0.1271,0.0256,0.0013</t>
-  </si>
-  <si>
-    <t>0.9195,0.0216,0.0334,0.0078</t>
-  </si>
-  <si>
-    <t>0.8623,0.1221,0.0200,0.0021</t>
-  </si>
-  <si>
-    <t>0.9686,0.0066,0.0124,0.0013</t>
-  </si>
-  <si>
-    <t>0.9823,0.0031,0.0107,0.0010</t>
-  </si>
-  <si>
-    <t>0.9624,0.0133,0.0035,0.0018</t>
-  </si>
-  <si>
-    <t>0.7869,0.1672,0.0141,0.0093</t>
-  </si>
-  <si>
-    <t>0.8629,0.1078,0.0040,0.0031</t>
-  </si>
-  <si>
-    <t>0.6920,0.2610,0.0205,0.0085</t>
-  </si>
-  <si>
-    <t>0.6821,0.1572,0.0096,0.0376</t>
-  </si>
-  <si>
-    <t>0.8202,0.1804,0.0058,0.0024</t>
-  </si>
-  <si>
-    <t>0.9258,0.0357,0.0168,0.0009</t>
-  </si>
-  <si>
-    <t>0.9519,0.0248,0.0101,0.0005</t>
-  </si>
-  <si>
-    <t>0.9551,0.0081,0.0259,0.0020</t>
-  </si>
-  <si>
-    <t>0.9629,0.0058,0.0283,0.0011</t>
-  </si>
-  <si>
-    <t>0.9005,0.0442,0.0241,0.0022</t>
-  </si>
-  <si>
-    <t>0.7082,0.1040,0.1520,0.0042</t>
-  </si>
-  <si>
-    <t>0.7661,0.0827,0.1850,0.0068</t>
-  </si>
-  <si>
-    <t>0.7264,0.1823,0.1023,0.0065</t>
-  </si>
-  <si>
-    <t>0.9089,0.0350,0.0423,0.0024</t>
-  </si>
-  <si>
-    <t>0.6082,0.1878,0.2408,0.0041</t>
-  </si>
-  <si>
-    <t>0.8949,0.0641,0.0066,0.0075</t>
-  </si>
-  <si>
-    <t>0.7659,0.1004,0.0182,0.0403</t>
-  </si>
-  <si>
-    <t>0.8548,0.0828,0.0225,0.0178</t>
-  </si>
-  <si>
-    <t>0.8905,0.0873,0.0077,0.0026</t>
-  </si>
-  <si>
-    <t>0.8629,0.0487,0.0123,0.0218</t>
-  </si>
-  <si>
-    <t>0.8677,0.1172,0.0105,0.0032</t>
-  </si>
-  <si>
-    <t>0.7417,0.1048,0.0228,0.0575</t>
-  </si>
-  <si>
-    <t>0.8517,0.1053,0.0101,0.0068</t>
-  </si>
-  <si>
-    <t>0.9725,0.0102,0.0079,0.0013</t>
-  </si>
-  <si>
-    <t>0.9282,0.0445,0.0132,0.0029</t>
-  </si>
-  <si>
-    <t>0.9106,0.0478,0.0267,0.0054</t>
-  </si>
-  <si>
-    <t>0.4736,0.2657,0.2955,0.0065</t>
-  </si>
-  <si>
-    <t>0.4452,0.4209,0.2025,0.0072</t>
-  </si>
-  <si>
-    <t>0.8106,0.1009,0.0716,0.0014</t>
-  </si>
-  <si>
-    <t>0.5687,0.0769,0.4098,0.0033</t>
-  </si>
-  <si>
-    <t>0.9789,0.0036,0.0158,0.0004</t>
-  </si>
-  <si>
-    <t>0.6281,0.0301,0.5186,0.0084</t>
-  </si>
-  <si>
-    <t>0.5346,0.3083,0.1826,0.0039</t>
-  </si>
-  <si>
-    <t>0.9664,0.0119,0.0102,0.0006</t>
-  </si>
-  <si>
-    <t>0.9512,0.0155,0.0098,0.0037</t>
-  </si>
-  <si>
-    <t>0.9688,0.0118,0.0077,0.0012</t>
-  </si>
-  <si>
-    <t>0.9832,0.0032,0.0065,0.0007</t>
-  </si>
-  <si>
-    <t>0.7624,0.0948,0.0089,0.0282</t>
-  </si>
-  <si>
-    <t>0.8789,0.0664,0.0165,0.0143</t>
-  </si>
-  <si>
-    <t>0.8060,0.0614,0.0202,0.0592</t>
-  </si>
-  <si>
-    <t>0.6539,0.1945,0.0256,0.0361</t>
-  </si>
-  <si>
-    <t>0.8042,0.0818,0.0074,0.0174</t>
-  </si>
-  <si>
-    <t>0.8566,0.0499,0.0092,0.0146</t>
-  </si>
-  <si>
-    <t>0.7679,0.1814,0.0102,0.0043</t>
-  </si>
-  <si>
-    <t>0.8890,0.0484,0.0179,0.0146</t>
-  </si>
-  <si>
-    <t>0.7116,0.1605,0.1358,0.0050</t>
-  </si>
-  <si>
-    <t>0.7998,0.0360,0.1732,0.0010</t>
-  </si>
-  <si>
-    <t>0.5884,0.1901,0.1802,0.0034</t>
-  </si>
-  <si>
-    <t>0.9460,0.0082,0.0572,0.0013</t>
-  </si>
-  <si>
-    <t>0.9259,0.0157,0.0761,0.0026</t>
-  </si>
-  <si>
-    <t>0.8976,0.0372,0.0391,0.0120</t>
-  </si>
-  <si>
-    <t>0.9736,0.0095,0.0095,0.0007</t>
-  </si>
-  <si>
-    <t>0.7130,0.1172,0.2078,0.0339</t>
-  </si>
-  <si>
-    <t>0.9578,0.0141,0.0049,0.0041</t>
-  </si>
-  <si>
-    <t>0.9091,0.0118,0.0155,0.0349</t>
-  </si>
-  <si>
-    <t>0.9478,0.0056,0.0139,0.0160</t>
-  </si>
-  <si>
-    <t>0.9531,0.0078,0.0222,0.0058</t>
-  </si>
-  <si>
-    <t>0.9240,0.0166,0.0180,0.0230</t>
-  </si>
-  <si>
-    <t>0.9487,0.0220,0.0139,0.0025</t>
+    <t>0.8328,0.1254,0.0061,0.0439</t>
+  </si>
+  <si>
+    <t>0.0134,0.0007,0.0014,0.9929</t>
+  </si>
+  <si>
+    <t>0.2231,0.0044,0.0049,0.8688</t>
+  </si>
+  <si>
+    <t>0.0239,0.0016,0.0043,0.9845</t>
+  </si>
+  <si>
+    <t>0.9963,0.0012,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9902,0.0028,0.0005,0.0025</t>
+  </si>
+  <si>
+    <t>0.9972,0.0008,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9910,0.0042,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.9938,0.0042,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9952,0.0018,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.7709,0.0526,0.1903,0.0050</t>
+  </si>
+  <si>
+    <t>0.1647,0.0229,0.8409,0.0088</t>
+  </si>
+  <si>
+    <t>0.5734,0.0272,0.4532,0.0013</t>
+  </si>
+  <si>
+    <t>0.0090,0.0093,0.9859,0.0005</t>
+  </si>
+  <si>
+    <t>0.4469,0.0180,0.6169,0.0051</t>
+  </si>
+  <si>
+    <t>0.0668,0.9607,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.0612,0.9573,0.0066,0.0007</t>
+  </si>
+  <si>
+    <t>0.3759,0.7901,0.0023,0.0008</t>
+  </si>
+  <si>
+    <t>0.1350,0.9412,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0089,0.9899,0.0058,0.0006</t>
+  </si>
+  <si>
+    <t>0.6191,0.0277,0.3726,0.0602</t>
+  </si>
+  <si>
+    <t>0.5698,0.0279,0.4001,0.0411</t>
+  </si>
+  <si>
+    <t>0.0525,0.0713,0.9027,0.0265</t>
+  </si>
+  <si>
+    <t>0.3318,0.0148,0.7083,0.0095</t>
+  </si>
+  <si>
+    <t>0.0298,0.0387,0.9444,0.0095</t>
+  </si>
+  <si>
+    <t>0.2598,0.0086,0.7872,0.0099</t>
+  </si>
+  <si>
+    <t>0.0132,0.0008,0.9850,0.0042</t>
+  </si>
+  <si>
+    <t>0.7346,0.4643,0.0041,0.0006</t>
+  </si>
+  <si>
+    <t>0.4570,0.2200,0.4086,0.0547</t>
+  </si>
+  <si>
+    <t>0.0006,0.0021,0.9948,0.0103</t>
+  </si>
+  <si>
+    <t>0.0274,0.9313,0.0678,0.0080</t>
+  </si>
+  <si>
+    <t>0.8771,0.0347,0.0413,0.0435</t>
+  </si>
+  <si>
+    <t>0.9184,0.0232,0.0469,0.0051</t>
+  </si>
+  <si>
+    <t>0.6980,0.3868,0.0294,0.0015</t>
+  </si>
+  <si>
+    <t>0.0024,0.9719,0.7124,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.9765,0.0215,0.0150</t>
+  </si>
+  <si>
+    <t>0.4345,0.0088,0.6234,0.0210</t>
+  </si>
+  <si>
+    <t>0.0781,0.0327,0.8883,0.0189</t>
+  </si>
+  <si>
+    <t>0.7537,0.0077,0.1078,0.1038</t>
+  </si>
+  <si>
+    <t>0.0814,0.2084,0.8725,0.0036</t>
+  </si>
+  <si>
+    <t>0.0098,0.9591,0.0247,0.0039</t>
+  </si>
+  <si>
+    <t>0.0281,0.0539,0.9378,0.0031</t>
+  </si>
+  <si>
+    <t>0.2467,0.3974,0.0695,0.5913</t>
+  </si>
+  <si>
+    <t>0.0252,0.9633,0.0316,0.0071</t>
+  </si>
+  <si>
+    <t>0.0169,0.9582,0.0345,0.0027</t>
+  </si>
+  <si>
+    <t>0.0024,0.9923,0.0436,0.0004</t>
+  </si>
+  <si>
+    <t>0.2592,0.0300,0.8516,0.0047</t>
+  </si>
+  <si>
+    <t>0.0036,0.1299,0.9877,0.0030</t>
+  </si>
+  <si>
+    <t>0.0167,0.0058,0.9703,0.0048</t>
+  </si>
+  <si>
+    <t>0.1094,0.0200,0.8813,0.0244</t>
+  </si>
+  <si>
+    <t>0.0093,0.0422,0.9875,0.0006</t>
+  </si>
+  <si>
+    <t>0.0076,0.0054,0.9895,0.0010</t>
+  </si>
+  <si>
+    <t>0.9433,0.0872,0.0058,0.0021</t>
+  </si>
+  <si>
+    <t>0.9926,0.0015,0.0058,0.0005</t>
+  </si>
+  <si>
+    <t>0.9708,0.0169,0.0060,0.0058</t>
+  </si>
+  <si>
+    <t>0.0045,0.1204,0.9747,0.0069</t>
+  </si>
+  <si>
+    <t>0.9948,0.0024,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9929,0.0048,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9616,0.0541,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.0084,0.6928,0.9493,0.0026</t>
+  </si>
+  <si>
+    <t>0.0105,0.6474,0.9522,0.0028</t>
+  </si>
+  <si>
+    <t>0.0203,0.0029,0.9756,0.0050</t>
+  </si>
+  <si>
+    <t>0.0035,0.9253,0.6180,0.0009</t>
+  </si>
+  <si>
+    <t>0.0116,0.0407,0.9800,0.0044</t>
+  </si>
+  <si>
+    <t>0.1464,0.8193,0.0866,0.0079</t>
+  </si>
+  <si>
+    <t>0.0480,0.9815,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9484,0.0067,0.0845,0.0029</t>
+  </si>
+  <si>
+    <t>0.6449,0.1176,0.3102,0.0067</t>
+  </si>
+  <si>
+    <t>0.0078,0.0315,0.9865,0.0037</t>
+  </si>
+  <si>
+    <t>0.0013,0.9137,0.8782,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.7398,0.9387,0.0007</t>
+  </si>
+  <si>
+    <t>0.0021,0.9925,0.0200,0.0010</t>
+  </si>
+  <si>
+    <t>0.0022,0.9239,0.9412,0.0010</t>
+  </si>
+  <si>
+    <t>0.0152,0.0007,0.0253,0.9785</t>
+  </si>
+  <si>
+    <t>0.0030,0.0009,0.0018,0.9972</t>
+  </si>
+  <si>
+    <t>0.0200,0.0013,0.0047,0.9879</t>
+  </si>
+  <si>
+    <t>0.0463,0.0160,0.0416,0.9507</t>
+  </si>
+  <si>
+    <t>0.0087,0.0064,0.0111,0.9886</t>
+  </si>
+  <si>
+    <t>0.0030,0.0194,0.0185,0.9897</t>
+  </si>
+  <si>
+    <t>0.0003,0.9892,0.8518,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.8570,0.9552,0.0003</t>
+  </si>
+  <si>
+    <t>0.0193,0.9007,0.1872,0.0024</t>
+  </si>
+  <si>
+    <t>0.0246,0.2263,0.9030,0.0095</t>
+  </si>
+  <si>
+    <t>0.0006,0.9623,0.8921,0.0002</t>
+  </si>
+  <si>
+    <t>0.0100,0.9184,0.1572,0.0028</t>
+  </si>
+  <si>
+    <t>0.9949,0.0013,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9894,0.0082,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.9934,0.0045,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9881,0.0028,0.0012,0.0046</t>
+  </si>
+  <si>
+    <t>0.9915,0.0069,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9962,0.0008,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9868,0.0119,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0005,0.0002,0.0042</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9886,0.0053,0.0027,0.0024</t>
+  </si>
+  <si>
+    <t>0.9964,0.0009,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.1301,0.0019,0.9510,0.0016</t>
+  </si>
+  <si>
+    <t>0.0263,0.0084,0.9723,0.0008</t>
+  </si>
+  <si>
+    <t>0.7731,0.0283,0.1087,0.1010</t>
+  </si>
+  <si>
+    <t>0.0069,0.0028,0.9886,0.0021</t>
+  </si>
+  <si>
+    <t>0.4433,0.6900,0.0021,0.0025</t>
+  </si>
+  <si>
+    <t>0.1186,0.9428,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.1448,0.9092,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.0163,0.9852,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.0422,0.9615,0.0110,0.0007</t>
+  </si>
+  <si>
+    <t>0.0112,0.9890,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.5860,0.6238,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.6976,0.1326,0.1516,0.0468</t>
+  </si>
+  <si>
+    <t>0.2506,0.0108,0.7934,0.0077</t>
+  </si>
+  <si>
+    <t>0.1532,0.4112,0.3908,0.0715</t>
+  </si>
+  <si>
+    <t>0.6851,0.0269,0.3356,0.0088</t>
+  </si>
+  <si>
+    <t>0.2723,0.4284,0.3986,0.2986</t>
+  </si>
+  <si>
+    <t>0.0026,0.9939,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.0121,0.9698,0.0350,0.0681</t>
+  </si>
+  <si>
+    <t>0.0005,0.9745,0.8425,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.9946,0.0132,0.0001</t>
+  </si>
+  <si>
+    <t>0.8177,0.2838,0.0142,0.0018</t>
+  </si>
+  <si>
+    <t>0.8842,0.1410,0.0133,0.0011</t>
+  </si>
+  <si>
+    <t>0.9809,0.0311,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9890,0.0036,0.0020,0.0029</t>
+  </si>
+  <si>
+    <t>0.9899,0.0013,0.0023,0.0030</t>
+  </si>
+  <si>
+    <t>0.9769,0.0124,0.0110,0.0048</t>
+  </si>
+  <si>
+    <t>0.9955,0.0019,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9938,0.0047,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.9901,0.0032,0.0017,0.0025</t>
+  </si>
+  <si>
+    <t>0.9874,0.0025,0.0013,0.0050</t>
+  </si>
+  <si>
+    <t>0.0025,0.1918,0.9462,0.0046</t>
+  </si>
+  <si>
+    <t>0.0011,0.7067,0.9776,0.0005</t>
+  </si>
+  <si>
+    <t>0.0292,0.0881,0.9165,0.0074</t>
+  </si>
+  <si>
+    <t>0.0033,0.3219,0.9801,0.0004</t>
+  </si>
+  <si>
+    <t>0.9228,0.0530,0.0069,0.0091</t>
+  </si>
+  <si>
+    <t>0.9790,0.0035,0.0101,0.0013</t>
+  </si>
+  <si>
+    <t>0.5188,0.0023,0.6650,0.0027</t>
+  </si>
+  <si>
+    <t>0.7760,0.0235,0.2414,0.0132</t>
+  </si>
+  <si>
+    <t>0.1167,0.0003,0.0006,0.9623</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.0021,0.9990</t>
+  </si>
+  <si>
+    <t>0.0015,0.0030,0.0004,0.9984</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0008,0.9995</t>
+  </si>
+  <si>
+    <t>0.0035,0.9629,0.1578,0.0032</t>
+  </si>
+  <si>
+    <t>0.9935,0.0014,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.1661,0.8988,0.0038,0.0040</t>
+  </si>
+  <si>
+    <t>0.9931,0.0027,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.7203,0.4584,0.0048,0.0012</t>
+  </si>
+  <si>
+    <t>0.9793,0.0045,0.0036,0.0079</t>
+  </si>
+  <si>
+    <t>0.4298,0.0225,0.0133,0.6315</t>
+  </si>
+  <si>
+    <t>0.9784,0.0044,0.0046,0.0083</t>
+  </si>
+  <si>
+    <t>0.0172,0.0206,0.9487,0.0506</t>
+  </si>
+  <si>
+    <t>0.9108,0.0024,0.0052,0.0983</t>
+  </si>
+  <si>
+    <t>0.7996,0.0117,0.0185,0.1996</t>
+  </si>
+  <si>
+    <t>0.6436,0.2515,0.1015,0.0089</t>
+  </si>
+  <si>
+    <t>0.9122,0.0386,0.0138,0.0228</t>
+  </si>
+  <si>
+    <t>0.9761,0.0156,0.0058,0.0022</t>
+  </si>
+  <si>
+    <t>0.1327,0.7092,0.2099,0.0450</t>
+  </si>
+  <si>
+    <t>0.9253,0.0958,0.0075,0.0020</t>
+  </si>
+  <si>
+    <t>0.9496,0.0315,0.0226,0.0038</t>
+  </si>
+  <si>
+    <t>0.9869,0.0019,0.0023,0.0058</t>
+  </si>
+  <si>
+    <t>0.9934,0.0015,0.0013,0.0020</t>
+  </si>
+  <si>
+    <t>0.9938,0.0014,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9962,0.0004,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9950,0.0009,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9941,0.0025,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9900,0.0010,0.0013,0.0045</t>
+  </si>
+  <si>
+    <t>0.9948,0.0005,0.0002,0.0024</t>
+  </si>
+  <si>
+    <t>0.8265,0.3365,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.7936,0.2542,0.0252,0.0027</t>
+  </si>
+  <si>
+    <t>0.8361,0.2189,0.0051,0.0027</t>
+  </si>
+  <si>
+    <t>0.0536,0.4558,0.8163,0.0202</t>
+  </si>
+  <si>
+    <t>0.9841,0.0166,0.0041,0.0009</t>
+  </si>
+  <si>
+    <t>0.9658,0.0297,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9866,0.0086,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.9789,0.0137,0.0014,0.0043</t>
+  </si>
+  <si>
+    <t>0.0011,0.1148,0.9924,0.0011</t>
+  </si>
+  <si>
+    <t>0.9607,0.0427,0.0075,0.0031</t>
+  </si>
+  <si>
+    <t>0.0072,0.0136,0.9863,0.0014</t>
+  </si>
+  <si>
+    <t>0.0208,0.0611,0.9659,0.0034</t>
+  </si>
+  <si>
+    <t>0.0433,0.0128,0.9558,0.0008</t>
+  </si>
+  <si>
+    <t>0.0120,0.1371,0.9762,0.0050</t>
+  </si>
+  <si>
+    <t>0.0029,0.0210,0.9839,0.0044</t>
+  </si>
+  <si>
+    <t>0.0065,0.0050,0.9846,0.0068</t>
+  </si>
+  <si>
+    <t>0.0044,0.0109,0.9915,0.0019</t>
+  </si>
+  <si>
+    <t>0.4895,0.0244,0.5852,0.0055</t>
+  </si>
+  <si>
+    <t>0.3237,0.0037,0.8237,0.0018</t>
+  </si>
+  <si>
+    <t>0.1021,0.0654,0.8279,0.0034</t>
+  </si>
+  <si>
+    <t>0.3805,0.0148,0.7041,0.0016</t>
+  </si>
+  <si>
+    <t>0.1537,0.0595,0.8402,0.0017</t>
+  </si>
+  <si>
+    <t>0.2407,0.2452,0.5393,0.0150</t>
+  </si>
+  <si>
+    <t>0.5969,0.0200,0.4627,0.0128</t>
+  </si>
+  <si>
+    <t>0.1643,0.5527,0.2880,0.0478</t>
+  </si>
+  <si>
+    <t>0.9758,0.0280,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.9240,0.1317,0.0023,0.0018</t>
+  </si>
+  <si>
+    <t>0.9851,0.0193,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9833,0.0206,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9761,0.0397,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.6197,0.1015,0.3397,0.0232</t>
+  </si>
+  <si>
+    <t>0.9332,0.0055,0.0842,0.0023</t>
+  </si>
+  <si>
+    <t>0.9434,0.0054,0.0315,0.0061</t>
+  </si>
+  <si>
+    <t>0.6600,0.0152,0.3437,0.0328</t>
+  </si>
+  <si>
+    <t>0.9390,0.0004,0.0795,0.0027</t>
+  </si>
+  <si>
+    <t>0.0053,0.0030,0.9793,0.0125</t>
+  </si>
+  <si>
+    <t>0.0078,0.8697,0.4462,0.0075</t>
+  </si>
+  <si>
+    <t>0.1705,0.3859,0.7026,0.0849</t>
+  </si>
+  <si>
+    <t>0.6001,0.0106,0.5138,0.0056</t>
+  </si>
+  <si>
+    <t>0.0052,0.7666,0.4615,0.0072</t>
+  </si>
+  <si>
+    <t>0.9745,0.0126,0.0043,0.0089</t>
+  </si>
+  <si>
+    <t>0.9946,0.0027,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9962,0.0011,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9866,0.0207,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9816,0.0236,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.9940,0.0033,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9908,0.0057,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9933,0.0022,0.0014,0.0018</t>
+  </si>
+  <si>
+    <t>0.0109,0.0693,0.9653,0.0044</t>
+  </si>
+  <si>
+    <t>0.1019,0.7938,0.1928,0.0053</t>
+  </si>
+  <si>
+    <t>0.9511,0.0095,0.0370,0.0035</t>
+  </si>
+  <si>
+    <t>0.0022,0.0035,0.9918,0.0045</t>
+  </si>
+  <si>
+    <t>0.0008,0.0075,0.9946,0.0045</t>
+  </si>
+  <si>
+    <t>0.0192,0.4517,0.8116,0.0135</t>
+  </si>
+  <si>
+    <t>0.0265,0.0064,0.9841,0.0008</t>
+  </si>
+  <si>
+    <t>0.1581,0.0210,0.8503,0.0047</t>
+  </si>
+  <si>
+    <t>0.0041,0.0355,0.9920,0.0024</t>
+  </si>
+  <si>
+    <t>0.1113,0.0548,0.8732,0.0191</t>
+  </si>
+  <si>
+    <t>0.0446,0.0297,0.9246,0.0074</t>
+  </si>
+  <si>
+    <t>0.9363,0.0016,0.0942,0.0036</t>
+  </si>
+  <si>
+    <t>0.6125,0.0019,0.4941,0.0112</t>
+  </si>
+  <si>
+    <t>0.9629,0.0043,0.0166,0.0084</t>
+  </si>
+  <si>
+    <t>0.9925,0.0043,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9970,0.0014,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9957,0.0011,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9949,0.0035,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0010,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9911,0.0090,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0014,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.0028,0.0239,0.9888,0.0010</t>
+  </si>
+  <si>
+    <t>0.0079,0.4681,0.9349,0.0027</t>
+  </si>
+  <si>
+    <t>0.0188,0.0617,0.9526,0.0079</t>
+  </si>
+  <si>
+    <t>0.0301,0.0341,0.9268,0.0107</t>
+  </si>
+  <si>
+    <t>0.2929,0.0115,0.8099,0.0029</t>
+  </si>
+  <si>
+    <t>0.1573,0.2786,0.3955,0.4769</t>
+  </si>
+  <si>
+    <t>0.2529,0.0674,0.7241,0.0405</t>
+  </si>
+  <si>
+    <t>0.0666,0.0597,0.8168,0.0695</t>
+  </si>
+  <si>
+    <t>0.8559,0.0003,0.0021,0.2153</t>
+  </si>
+  <si>
+    <t>0.0754,0.0167,0.0151,0.9441</t>
+  </si>
+  <si>
+    <t>0.2080,0.0047,0.0063,0.8857</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.0119,0.9978</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.5746,0.0045,0.0061,0.5408</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1981,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2177,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
         <v>280</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
@@ -5509,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
         <v>518</v>
